--- a/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-inf-item.xlsx
+++ b/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-inf-item.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.5.0</t>
+    <t>1.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-10T06:36:19+00:00</t>
+    <t>2026-08-28T11:20:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1245,7 +1245,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>95</v>
       </c>
@@ -1350,7 +1350,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" hidden="true">
+    <row r="6">
       <c r="A6" t="s" s="2">
         <v>101</v>
       </c>
@@ -1455,7 +1455,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>106</v>
       </c>
@@ -1560,7 +1560,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>111</v>
       </c>
@@ -1665,7 +1665,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
         <v>116</v>
       </c>
@@ -1770,7 +1770,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>121</v>
       </c>
@@ -1875,7 +1875,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>126</v>
       </c>
@@ -2190,12 +2190,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AK13">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-inf-item.xlsx
+++ b/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-inf-item.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.6.0</t>
+    <t>1.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T11:20:46+00:00</t>
+    <t>2026-08-28T12:05:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-inf-item.xlsx
+++ b/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-inf-item.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.5.0</t>
+    <t>1.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:05:03+00:00</t>
+    <t>2026-08-28T12:17:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-inf-item.xlsx
+++ b/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-inf-item.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:17:39+00:00</t>
+    <t>2026-08-31T14:07:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
